--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202604/AllSymbols_P&L_20260429.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202604/AllSymbols_P&L_20260429.xlsx
@@ -735,13 +735,13 @@
         <v>2000</v>
       </c>
       <c r="C2">
-        <v>30.94</v>
+        <v>32.96</v>
       </c>
       <c r="D2">
-        <v>-112.31</v>
+        <v>515.5</v>
       </c>
       <c r="E2">
-        <v>61880</v>
+        <v>65920</v>
       </c>
       <c r="F2" t="s">
         <v>100</v>
@@ -753,7 +753,7 @@
         <v>0.1276</v>
       </c>
       <c r="I2">
-        <v>7895.89</v>
+        <v>8411.389999999999</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -764,13 +764,13 @@
         <v>427000</v>
       </c>
       <c r="C3">
-        <v>13.17</v>
+        <v>13.69</v>
       </c>
       <c r="D3">
-        <v>-6539.25</v>
+        <v>28332.3</v>
       </c>
       <c r="E3">
-        <v>5623590</v>
+        <v>5845630</v>
       </c>
       <c r="F3" t="s">
         <v>100</v>
@@ -782,7 +782,7 @@
         <v>0.1276</v>
       </c>
       <c r="I3">
-        <v>717570.08</v>
+        <v>745902.39</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -822,13 +822,13 @@
         <v>6000</v>
       </c>
       <c r="C5">
-        <v>7.18</v>
+        <v>7.22</v>
       </c>
       <c r="D5">
-        <v>-30.63</v>
+        <v>30.62</v>
       </c>
       <c r="E5">
-        <v>43080</v>
+        <v>43320</v>
       </c>
       <c r="F5" t="s">
         <v>100</v>
@@ -840,7 +840,7 @@
         <v>0.1276</v>
       </c>
       <c r="I5">
-        <v>5497.01</v>
+        <v>5527.63</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -851,13 +851,13 @@
         <v>2000</v>
       </c>
       <c r="C6">
-        <v>35.92</v>
+        <v>36.58</v>
       </c>
       <c r="D6">
-        <v>-153.14</v>
+        <v>168.43</v>
       </c>
       <c r="E6">
-        <v>71840</v>
+        <v>73160</v>
       </c>
       <c r="F6" t="s">
         <v>100</v>
@@ -869,7 +869,7 @@
         <v>0.1276</v>
       </c>
       <c r="I6">
-        <v>9166.780000000001</v>
+        <v>9335.219999999999</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -880,13 +880,13 @@
         <v>200</v>
       </c>
       <c r="C7">
-        <v>29.92</v>
+        <v>30.14</v>
       </c>
       <c r="D7">
-        <v>-30.12</v>
+        <v>5.61</v>
       </c>
       <c r="E7">
-        <v>5984</v>
+        <v>6028</v>
       </c>
       <c r="F7" t="s">
         <v>100</v>
@@ -898,7 +898,7 @@
         <v>0.1276</v>
       </c>
       <c r="I7">
-        <v>763.5599999999999</v>
+        <v>769.17</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -909,13 +909,13 @@
         <v>300</v>
       </c>
       <c r="C8">
-        <v>143.1</v>
+        <v>137.8</v>
       </c>
       <c r="D8">
-        <v>654.6900000000001</v>
+        <v>-202.88</v>
       </c>
       <c r="E8">
-        <v>42930</v>
+        <v>41340</v>
       </c>
       <c r="F8" t="s">
         <v>100</v>
@@ -927,7 +927,7 @@
         <v>0.1276</v>
       </c>
       <c r="I8">
-        <v>5477.87</v>
+        <v>5274.98</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -938,13 +938,13 @@
         <v>2000</v>
       </c>
       <c r="C9">
-        <v>25.98</v>
+        <v>26.24</v>
       </c>
       <c r="D9">
-        <v>-66.36</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="E9">
-        <v>51960</v>
+        <v>52480</v>
       </c>
       <c r="F9" t="s">
         <v>100</v>
@@ -956,7 +956,7 @@
         <v>0.1276</v>
       </c>
       <c r="I9">
-        <v>6630.1</v>
+        <v>6696.45</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -967,13 +967,13 @@
         <v>600</v>
       </c>
       <c r="C10">
-        <v>88.45999999999999</v>
+        <v>91</v>
       </c>
       <c r="D10">
-        <v>-102.61</v>
+        <v>194.46</v>
       </c>
       <c r="E10">
-        <v>53076</v>
+        <v>54600</v>
       </c>
       <c r="F10" t="s">
         <v>100</v>
@@ -985,7 +985,7 @@
         <v>0.1276</v>
       </c>
       <c r="I10">
-        <v>6772.5</v>
+        <v>6966.96</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -996,13 +996,13 @@
         <v>110000</v>
       </c>
       <c r="C11">
-        <v>35.36</v>
+        <v>36.46</v>
       </c>
       <c r="D11">
-        <v>-12072.85</v>
+        <v>15439.6</v>
       </c>
       <c r="E11">
-        <v>3889600</v>
+        <v>4010600</v>
       </c>
       <c r="F11" t="s">
         <v>100</v>
@@ -1014,7 +1014,7 @@
         <v>0.1276</v>
       </c>
       <c r="I11">
-        <v>496312.96</v>
+        <v>511752.56</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1025,13 +1025,13 @@
         <v>700</v>
       </c>
       <c r="C12">
-        <v>10.15</v>
+        <v>10.31</v>
       </c>
       <c r="D12">
-        <v>-22.33</v>
+        <v>14.29</v>
       </c>
       <c r="E12">
-        <v>7105</v>
+        <v>7217</v>
       </c>
       <c r="F12" t="s">
         <v>100</v>
@@ -1043,7 +1043,7 @@
         <v>0.1276</v>
       </c>
       <c r="I12">
-        <v>906.6</v>
+        <v>920.89</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1054,13 +1054,13 @@
         <v>4700</v>
       </c>
       <c r="C13">
-        <v>629</v>
+        <v>627.5</v>
       </c>
       <c r="D13">
-        <v>-27891.35</v>
+        <v>-899.58</v>
       </c>
       <c r="E13">
-        <v>2956300</v>
+        <v>2949250</v>
       </c>
       <c r="F13" t="s">
         <v>100</v>
@@ -1072,7 +1072,7 @@
         <v>0.1276</v>
       </c>
       <c r="I13">
-        <v>377223.88</v>
+        <v>376324.3</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1083,13 +1083,13 @@
         <v>23500</v>
       </c>
       <c r="C14">
-        <v>407.6</v>
+        <v>419.8</v>
       </c>
       <c r="D14">
-        <v>-13195.91</v>
+        <v>36582.92</v>
       </c>
       <c r="E14">
-        <v>9578600</v>
+        <v>9865300</v>
       </c>
       <c r="F14" t="s">
         <v>100</v>
@@ -1101,7 +1101,7 @@
         <v>0.1276</v>
       </c>
       <c r="I14">
-        <v>1222229.36</v>
+        <v>1258812.28</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1112,13 +1112,13 @@
         <v>4000</v>
       </c>
       <c r="C15">
-        <v>5.12</v>
+        <v>5.18</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>30.62</v>
       </c>
       <c r="E15">
-        <v>20480</v>
+        <v>20720</v>
       </c>
       <c r="F15" t="s">
         <v>100</v>
@@ -1130,7 +1130,7 @@
         <v>0.1276</v>
       </c>
       <c r="I15">
-        <v>2613.25</v>
+        <v>2643.87</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1144,7 +1144,7 @@
         <v>6856</v>
       </c>
       <c r="D16">
-        <v>-43567.44</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>242016800</v>
@@ -1156,10 +1156,10 @@
         <v>104</v>
       </c>
       <c r="H16">
-        <v>0.0063</v>
+        <v>0.0062</v>
       </c>
       <c r="I16">
-        <v>1524705.84</v>
+        <v>1500504.16</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1170,13 +1170,13 @@
         <v>200</v>
       </c>
       <c r="C17">
-        <v>473.8</v>
+        <v>479.2</v>
       </c>
       <c r="D17">
-        <v>-122.52</v>
+        <v>137.81</v>
       </c>
       <c r="E17">
-        <v>94760</v>
+        <v>95840</v>
       </c>
       <c r="F17" t="s">
         <v>100</v>
@@ -1188,7 +1188,7 @@
         <v>0.1276</v>
       </c>
       <c r="I17">
-        <v>12091.38</v>
+        <v>12229.18</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1199,13 +1199,13 @@
         <v>16000</v>
       </c>
       <c r="C18">
-        <v>7.3</v>
+        <v>7.42</v>
       </c>
       <c r="D18">
-        <v>-61.26</v>
+        <v>244.99</v>
       </c>
       <c r="E18">
-        <v>116800</v>
+        <v>118720</v>
       </c>
       <c r="F18" t="s">
         <v>100</v>
@@ -1217,7 +1217,7 @@
         <v>0.1276</v>
       </c>
       <c r="I18">
-        <v>14903.68</v>
+        <v>15148.67</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1231,7 +1231,7 @@
         <v>7922</v>
       </c>
       <c r="D19">
-        <v>3397.51</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>148141400</v>
@@ -1243,10 +1243,10 @@
         <v>104</v>
       </c>
       <c r="H19">
-        <v>0.0063</v>
+        <v>0.0062</v>
       </c>
       <c r="I19">
-        <v>933290.8199999999</v>
+        <v>918476.6800000001</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1260,7 +1260,7 @@
         <v>689</v>
       </c>
       <c r="D20">
-        <v>4398.03</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>12402000</v>
@@ -1272,10 +1272,10 @@
         <v>104</v>
       </c>
       <c r="H20">
-        <v>0.0063</v>
+        <v>0.0062</v>
       </c>
       <c r="I20">
-        <v>78132.60000000001</v>
+        <v>76892.39999999999</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1289,7 +1289,7 @@
         <v>5500</v>
       </c>
       <c r="D21">
-        <v>4736.34</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>11550000</v>
@@ -1301,10 +1301,10 @@
         <v>104</v>
       </c>
       <c r="H21">
-        <v>0.0063</v>
+        <v>0.0062</v>
       </c>
       <c r="I21">
-        <v>72765</v>
+        <v>71610</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1315,13 +1315,13 @@
         <v>342000</v>
       </c>
       <c r="C22">
-        <v>11.67</v>
+        <v>11.98</v>
       </c>
       <c r="D22">
-        <v>9165.67</v>
+        <v>13528.15</v>
       </c>
       <c r="E22">
-        <v>3991140</v>
+        <v>4097160</v>
       </c>
       <c r="F22" t="s">
         <v>100</v>
@@ -1333,7 +1333,7 @@
         <v>0.1276</v>
       </c>
       <c r="I22">
-        <v>509269.46</v>
+        <v>522797.62</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1344,13 +1344,13 @@
         <v>106000</v>
       </c>
       <c r="C23">
-        <v>28.98</v>
+        <v>29.38</v>
       </c>
       <c r="D23">
-        <v>7304.97</v>
+        <v>5410.24</v>
       </c>
       <c r="E23">
-        <v>3071880</v>
+        <v>3114280</v>
       </c>
       <c r="F23" t="s">
         <v>100</v>
@@ -1362,7 +1362,7 @@
         <v>0.1276</v>
       </c>
       <c r="I23">
-        <v>391971.89</v>
+        <v>397382.13</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1373,13 +1373,13 @@
         <v>1800</v>
       </c>
       <c r="C24">
-        <v>46.5</v>
+        <v>48.18</v>
       </c>
       <c r="D24">
-        <v>-96.48</v>
+        <v>385.86</v>
       </c>
       <c r="E24">
-        <v>83700</v>
+        <v>86724</v>
       </c>
       <c r="F24" t="s">
         <v>100</v>
@@ -1391,7 +1391,7 @@
         <v>0.1276</v>
       </c>
       <c r="I24">
-        <v>10680.12</v>
+        <v>11065.98</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1402,13 +1402,13 @@
         <v>6000</v>
       </c>
       <c r="C25">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="D25">
-        <v>-93.97</v>
+        <v>-140.47</v>
       </c>
       <c r="E25">
-        <v>15120</v>
+        <v>14940</v>
       </c>
       <c r="F25" t="s">
         <v>102</v>
@@ -1417,10 +1417,10 @@
         <v>104</v>
       </c>
       <c r="H25">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I25">
-        <v>11840.47</v>
+        <v>11659.18</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1431,13 +1431,13 @@
         <v>3520</v>
       </c>
       <c r="C26">
-        <v>303.35</v>
+        <v>302.5</v>
       </c>
       <c r="D26">
-        <v>3414.4</v>
+        <v>-2992</v>
       </c>
       <c r="E26">
-        <v>1067792</v>
+        <v>1064800</v>
       </c>
       <c r="F26" t="s">
         <v>103</v>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1067792</v>
+        <v>1064800</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1460,13 +1460,13 @@
         <v>1362</v>
       </c>
       <c r="C27">
-        <v>192.34</v>
+        <v>183.5</v>
       </c>
       <c r="D27">
-        <v>-4630.8</v>
+        <v>-12040.08</v>
       </c>
       <c r="E27">
-        <v>261967.08</v>
+        <v>249927</v>
       </c>
       <c r="F27" t="s">
         <v>103</v>
@@ -1478,7 +1478,7 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>261967.08</v>
+        <v>249927</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1489,13 +1489,13 @@
         <v>18900</v>
       </c>
       <c r="C28">
-        <v>104.65</v>
+        <v>103.66</v>
       </c>
       <c r="D28">
-        <v>1701</v>
+        <v>-18711</v>
       </c>
       <c r="E28">
-        <v>1977885</v>
+        <v>1959174</v>
       </c>
       <c r="F28" t="s">
         <v>103</v>
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>1977885</v>
+        <v>1959174</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1518,13 +1518,13 @@
         <v>22075</v>
       </c>
       <c r="C29">
-        <v>88.81999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="D29">
-        <v>-14790.25</v>
+        <v>-5518.75</v>
       </c>
       <c r="E29">
-        <v>1960701.5</v>
+        <v>1955182.75</v>
       </c>
       <c r="F29" t="s">
         <v>103</v>
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1960701.5</v>
+        <v>1955182.75</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1547,13 +1547,13 @@
         <v>14660</v>
       </c>
       <c r="C30">
-        <v>119.44</v>
+        <v>118.6</v>
       </c>
       <c r="D30">
-        <v>-2492.2</v>
+        <v>-12314.4</v>
       </c>
       <c r="E30">
-        <v>1750990.4</v>
+        <v>1738676</v>
       </c>
       <c r="F30" t="s">
         <v>103</v>
@@ -1565,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>1750990.4</v>
+        <v>1738676</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1576,13 +1576,13 @@
         <v>14901</v>
       </c>
       <c r="C31">
-        <v>130.85</v>
+        <v>130.43</v>
       </c>
       <c r="D31">
-        <v>-24884.67</v>
+        <v>-6258.42</v>
       </c>
       <c r="E31">
-        <v>1949795.85</v>
+        <v>1943537.43</v>
       </c>
       <c r="F31" t="s">
         <v>103</v>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>1949795.85</v>
+        <v>1943537.43</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1605,13 +1605,13 @@
         <v>70</v>
       </c>
       <c r="C32">
-        <v>21.48</v>
+        <v>20.66</v>
       </c>
       <c r="D32">
-        <v>-4.9</v>
+        <v>-57.4</v>
       </c>
       <c r="E32">
-        <v>1503.6</v>
+        <v>1446.2</v>
       </c>
       <c r="F32" t="s">
         <v>103</v>
@@ -1623,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>1503.6</v>
+        <v>1446.2</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1634,13 +1634,13 @@
         <v>3000</v>
       </c>
       <c r="C33">
-        <v>10.89</v>
+        <v>10.8</v>
       </c>
       <c r="D33">
-        <v>-140.95</v>
+        <v>-210.7</v>
       </c>
       <c r="E33">
-        <v>32670</v>
+        <v>32400</v>
       </c>
       <c r="F33" t="s">
         <v>102</v>
@@ -1649,10 +1649,10 @@
         <v>104</v>
       </c>
       <c r="H33">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I33">
-        <v>25583.88</v>
+        <v>25284.96</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1663,13 +1663,13 @@
         <v>821</v>
       </c>
       <c r="C34">
-        <v>216.18</v>
+        <v>208.08</v>
       </c>
       <c r="D34">
-        <v>-4835.69</v>
+        <v>-6650.1</v>
       </c>
       <c r="E34">
-        <v>177483.78</v>
+        <v>170833.68</v>
       </c>
       <c r="F34" t="s">
         <v>103</v>
@@ -1681,7 +1681,7 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>177483.78</v>
+        <v>170833.68</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1692,13 +1692,13 @@
         <v>200</v>
       </c>
       <c r="C35">
-        <v>6.36</v>
+        <v>6.31</v>
       </c>
       <c r="D35">
-        <v>-1.57</v>
+        <v>-7.8</v>
       </c>
       <c r="E35">
-        <v>1272</v>
+        <v>1262</v>
       </c>
       <c r="F35" t="s">
         <v>102</v>
@@ -1707,10 +1707,10 @@
         <v>104</v>
       </c>
       <c r="H35">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I35">
-        <v>996.1</v>
+        <v>984.86</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1721,13 +1721,13 @@
         <v>15</v>
       </c>
       <c r="C36">
-        <v>305.71</v>
+        <v>297</v>
       </c>
       <c r="D36">
-        <v>-141.9</v>
+        <v>-130.65</v>
       </c>
       <c r="E36">
-        <v>4585.65</v>
+        <v>4455</v>
       </c>
       <c r="F36" t="s">
         <v>103</v>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>4585.65</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1750,13 +1750,13 @@
         <v>8000</v>
       </c>
       <c r="C37">
-        <v>122.31</v>
+        <v>126.78</v>
       </c>
       <c r="D37">
-        <v>-10560</v>
+        <v>35760</v>
       </c>
       <c r="E37">
-        <v>978480</v>
+        <v>1014240</v>
       </c>
       <c r="F37" t="s">
         <v>103</v>
@@ -1768,7 +1768,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>978480</v>
+        <v>1014240</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1782,7 +1782,7 @@
         <v>31.02</v>
       </c>
       <c r="D38">
-        <v>-138521.04</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>20461536.48</v>
@@ -1808,13 +1808,13 @@
         <v>29</v>
       </c>
       <c r="C39">
-        <v>284.53</v>
+        <v>287.27</v>
       </c>
       <c r="D39">
-        <v>75.11</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="E39">
-        <v>8251.370000000001</v>
+        <v>8330.83</v>
       </c>
       <c r="F39" t="s">
         <v>103</v>
@@ -1826,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="I39">
-        <v>8251.370000000001</v>
+        <v>8330.83</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1837,13 +1837,13 @@
         <v>27000</v>
       </c>
       <c r="C40">
-        <v>46.36</v>
+        <v>47.21</v>
       </c>
       <c r="D40">
-        <v>36180</v>
+        <v>22950</v>
       </c>
       <c r="E40">
-        <v>1251720</v>
+        <v>1274670</v>
       </c>
       <c r="F40" t="s">
         <v>103</v>
@@ -1855,7 +1855,7 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>1251720</v>
+        <v>1274670</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1866,13 +1866,13 @@
         <v>103455</v>
       </c>
       <c r="C41">
-        <v>50.8</v>
+        <v>51.85</v>
       </c>
       <c r="D41">
-        <v>-43523.52</v>
+        <v>108627.75</v>
       </c>
       <c r="E41">
-        <v>5255514</v>
+        <v>5364141.75</v>
       </c>
       <c r="F41" t="s">
         <v>103</v>
@@ -1884,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="I41">
-        <v>5255514</v>
+        <v>5364141.75</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1895,13 +1895,13 @@
         <v>5</v>
       </c>
       <c r="C42">
-        <v>194.1</v>
+        <v>181.73</v>
       </c>
       <c r="D42">
-        <v>-12.9</v>
+        <v>-61.85</v>
       </c>
       <c r="E42">
-        <v>970.5</v>
+        <v>908.65</v>
       </c>
       <c r="F42" t="s">
         <v>103</v>
@@ -1913,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>970.5</v>
+        <v>908.65</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1924,13 +1924,13 @@
         <v>45862</v>
       </c>
       <c r="C43">
-        <v>38.68</v>
+        <v>38.43</v>
       </c>
       <c r="D43">
-        <v>-32562.02</v>
+        <v>-11465.5</v>
       </c>
       <c r="E43">
-        <v>1773942.16</v>
+        <v>1762476.66</v>
       </c>
       <c r="F43" t="s">
         <v>103</v>
@@ -1942,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>1773942.16</v>
+        <v>1762476.66</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -1953,13 +1953,13 @@
         <v>22500</v>
       </c>
       <c r="C44">
-        <v>78.69</v>
+        <v>77.73</v>
       </c>
       <c r="D44">
-        <v>-67725</v>
+        <v>-21600</v>
       </c>
       <c r="E44">
-        <v>1770525</v>
+        <v>1748925</v>
       </c>
       <c r="F44" t="s">
         <v>103</v>
@@ -1971,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>1770525</v>
+        <v>1748925</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -1982,13 +1982,13 @@
         <v>13</v>
       </c>
       <c r="C45">
-        <v>86.86</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="D45">
-        <v>-18.2</v>
+        <v>35.23</v>
       </c>
       <c r="E45">
-        <v>1129.18</v>
+        <v>1164.41</v>
       </c>
       <c r="F45" t="s">
         <v>103</v>
@@ -2000,7 +2000,7 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>1129.18</v>
+        <v>1164.41</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2011,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="C46">
-        <v>174.22</v>
+        <v>173.95</v>
       </c>
       <c r="D46">
-        <v>1.8</v>
+        <v>-2.7</v>
       </c>
       <c r="E46">
-        <v>1742.2</v>
+        <v>1739.5</v>
       </c>
       <c r="F46" t="s">
         <v>103</v>
@@ -2029,7 +2029,7 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>1742.2</v>
+        <v>1739.5</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2040,13 +2040,13 @@
         <v>361</v>
       </c>
       <c r="C47">
-        <v>188.36</v>
+        <v>192.22</v>
       </c>
       <c r="D47">
-        <v>1292.38</v>
+        <v>1393.46</v>
       </c>
       <c r="E47">
-        <v>67997.96000000001</v>
+        <v>69391.42</v>
       </c>
       <c r="F47" t="s">
         <v>103</v>
@@ -2058,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>67997.96000000001</v>
+        <v>69391.42</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2069,13 +2069,13 @@
         <v>800</v>
       </c>
       <c r="C48">
-        <v>56.75</v>
+        <v>56.56</v>
       </c>
       <c r="D48">
-        <v>-25.06</v>
+        <v>-118.62</v>
       </c>
       <c r="E48">
-        <v>45400</v>
+        <v>45248</v>
       </c>
       <c r="F48" t="s">
         <v>102</v>
@@ -2084,10 +2084,10 @@
         <v>104</v>
       </c>
       <c r="H48">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I48">
-        <v>35552.74</v>
+        <v>35311.54</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2098,13 +2098,13 @@
         <v>612026</v>
       </c>
       <c r="C49">
-        <v>30.72</v>
+        <v>31.12</v>
       </c>
       <c r="D49">
-        <v>61202.6</v>
+        <v>244810.4</v>
       </c>
       <c r="E49">
-        <v>18801438.72</v>
+        <v>19046249.12</v>
       </c>
       <c r="F49" t="s">
         <v>103</v>
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>18801438.72</v>
+        <v>19046249.12</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2127,13 +2127,13 @@
         <v>401</v>
       </c>
       <c r="C50">
-        <v>563.86</v>
+        <v>560.02</v>
       </c>
       <c r="D50">
-        <v>-1535.83</v>
+        <v>-1539.84</v>
       </c>
       <c r="E50">
-        <v>226107.86</v>
+        <v>224568.02</v>
       </c>
       <c r="F50" t="s">
         <v>103</v>
@@ -2145,7 +2145,7 @@
         <v>1</v>
       </c>
       <c r="I50">
-        <v>226107.86</v>
+        <v>224568.02</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2156,13 +2156,13 @@
         <v>5000</v>
       </c>
       <c r="C51">
-        <v>115.82</v>
+        <v>114.13</v>
       </c>
       <c r="D51">
-        <v>-7650</v>
+        <v>-8450</v>
       </c>
       <c r="E51">
-        <v>579100</v>
+        <v>570650</v>
       </c>
       <c r="F51" t="s">
         <v>103</v>
@@ -2174,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="I51">
-        <v>579100</v>
+        <v>570650</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2185,13 +2185,13 @@
         <v>1</v>
       </c>
       <c r="C52">
-        <v>100.96</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="D52">
-        <v>-0.42</v>
+        <v>-1.03</v>
       </c>
       <c r="E52">
-        <v>100.96</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F52" t="s">
         <v>103</v>
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="I52">
-        <v>100.96</v>
+        <v>99.93000000000001</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2214,13 +2214,13 @@
         <v>36</v>
       </c>
       <c r="C53">
-        <v>138.42</v>
+        <v>136.56</v>
       </c>
       <c r="D53">
-        <v>-109.8</v>
+        <v>-66.95999999999999</v>
       </c>
       <c r="E53">
-        <v>4983.12</v>
+        <v>4916.16</v>
       </c>
       <c r="F53" t="s">
         <v>103</v>
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>4983.12</v>
+        <v>4916.16</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2243,13 +2243,13 @@
         <v>17</v>
       </c>
       <c r="C54">
-        <v>413.07</v>
+        <v>410.77</v>
       </c>
       <c r="D54">
-        <v>-62.9</v>
+        <v>-39.1</v>
       </c>
       <c r="E54">
-        <v>7022.19</v>
+        <v>6983.09</v>
       </c>
       <c r="F54" t="s">
         <v>103</v>
@@ -2261,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="I54">
-        <v>7022.19</v>
+        <v>6983.09</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2272,13 +2272,13 @@
         <v>30900</v>
       </c>
       <c r="C55">
-        <v>154.37</v>
+        <v>153.96</v>
       </c>
       <c r="D55">
-        <v>-72924</v>
+        <v>-12669</v>
       </c>
       <c r="E55">
-        <v>4770033</v>
+        <v>4757364</v>
       </c>
       <c r="F55" t="s">
         <v>103</v>
@@ -2290,7 +2290,7 @@
         <v>1</v>
       </c>
       <c r="I55">
-        <v>4770033</v>
+        <v>4757364</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2301,13 +2301,13 @@
         <v>76000</v>
       </c>
       <c r="C56">
-        <v>39.69</v>
+        <v>38.65</v>
       </c>
       <c r="D56">
-        <v>-15200</v>
+        <v>-79040</v>
       </c>
       <c r="E56">
-        <v>3016440</v>
+        <v>2937400</v>
       </c>
       <c r="F56" t="s">
         <v>103</v>
@@ -2319,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="I56">
-        <v>3016440</v>
+        <v>2937400</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2330,13 +2330,13 @@
         <v>1662</v>
       </c>
       <c r="C57">
-        <v>1088.93</v>
+        <v>1063.11</v>
       </c>
       <c r="D57">
-        <v>-52020.6</v>
+        <v>-42912.84</v>
       </c>
       <c r="E57">
-        <v>1809801.66</v>
+        <v>1766888.82</v>
       </c>
       <c r="F57" t="s">
         <v>103</v>
@@ -2348,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>1809801.66</v>
+        <v>1766888.82</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2359,13 +2359,13 @@
         <v>21300</v>
       </c>
       <c r="C58">
-        <v>34.75</v>
+        <v>34.47</v>
       </c>
       <c r="D58">
-        <v>639</v>
+        <v>-5964</v>
       </c>
       <c r="E58">
-        <v>740175</v>
+        <v>734211</v>
       </c>
       <c r="F58" t="s">
         <v>103</v>
@@ -2377,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>740175</v>
+        <v>734211</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2388,13 +2388,13 @@
         <v>611000</v>
       </c>
       <c r="C59">
-        <v>31.99</v>
+        <v>32.42</v>
       </c>
       <c r="D59">
-        <v>36660</v>
+        <v>262730</v>
       </c>
       <c r="E59">
-        <v>19545890</v>
+        <v>19808620</v>
       </c>
       <c r="F59" t="s">
         <v>103</v>
@@ -2406,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>19545890</v>
+        <v>19808620</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2417,13 +2417,13 @@
         <v>42</v>
       </c>
       <c r="C60">
-        <v>156.3</v>
+        <v>156.19</v>
       </c>
       <c r="D60">
-        <v>-27.3</v>
+        <v>-4.62</v>
       </c>
       <c r="E60">
-        <v>6564.6</v>
+        <v>6559.98</v>
       </c>
       <c r="F60" t="s">
         <v>103</v>
@@ -2435,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>6564.6</v>
+        <v>6559.98</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="C61">
-        <v>311.45</v>
+        <v>309.25</v>
       </c>
       <c r="D61">
-        <v>-3.6</v>
+        <v>-44</v>
       </c>
       <c r="E61">
-        <v>6229</v>
+        <v>6185</v>
       </c>
       <c r="F61" t="s">
         <v>103</v>
@@ -2464,7 +2464,7 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>6229</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2475,13 +2475,13 @@
         <v>558200</v>
       </c>
       <c r="C62">
-        <v>29.47</v>
+        <v>29.94</v>
       </c>
       <c r="D62">
-        <v>145132</v>
+        <v>262354</v>
       </c>
       <c r="E62">
-        <v>16450154</v>
+        <v>16712508</v>
       </c>
       <c r="F62" t="s">
         <v>103</v>
@@ -2493,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="I62">
-        <v>16450154</v>
+        <v>16712508</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -2504,13 +2504,13 @@
         <v>3800</v>
       </c>
       <c r="C63">
-        <v>525.8099999999999</v>
+        <v>521.61</v>
       </c>
       <c r="D63">
-        <v>-95722</v>
+        <v>-15960</v>
       </c>
       <c r="E63">
-        <v>1998078</v>
+        <v>1982118</v>
       </c>
       <c r="F63" t="s">
         <v>103</v>
@@ -2522,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>1998078</v>
+        <v>1982118</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -2533,13 +2533,13 @@
         <v>1451</v>
       </c>
       <c r="C64">
-        <v>70.37</v>
+        <v>69.03</v>
       </c>
       <c r="D64">
-        <v>435.3</v>
+        <v>-1944.34</v>
       </c>
       <c r="E64">
-        <v>102106.87</v>
+        <v>100162.53</v>
       </c>
       <c r="F64" t="s">
         <v>103</v>
@@ -2551,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="I64">
-        <v>102106.87</v>
+        <v>100162.53</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -2562,13 +2562,13 @@
         <v>1794</v>
       </c>
       <c r="C65">
-        <v>4.92</v>
+        <v>4.95</v>
       </c>
       <c r="D65">
-        <v>-592.02</v>
+        <v>53.82</v>
       </c>
       <c r="E65">
-        <v>8826.48</v>
+        <v>8880.299999999999</v>
       </c>
       <c r="F65" t="s">
         <v>103</v>
@@ -2580,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>8826.48</v>
+        <v>8880.299999999999</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -2591,13 +2591,13 @@
         <v>4000</v>
       </c>
       <c r="C66">
-        <v>510.29</v>
+        <v>504.71</v>
       </c>
       <c r="D66">
-        <v>-1840</v>
+        <v>-22320</v>
       </c>
       <c r="E66">
-        <v>2041160</v>
+        <v>2018840</v>
       </c>
       <c r="F66" t="s">
         <v>103</v>
@@ -2609,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>2041160</v>
+        <v>2018840</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -2620,13 +2620,13 @@
         <v>3</v>
       </c>
       <c r="C67">
-        <v>874</v>
+        <v>851.21</v>
       </c>
       <c r="D67">
-        <v>17.19</v>
+        <v>-68.37</v>
       </c>
       <c r="E67">
-        <v>2622</v>
+        <v>2553.63</v>
       </c>
       <c r="F67" t="s">
         <v>103</v>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="I67">
-        <v>2622</v>
+        <v>2553.63</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -2649,13 +2649,13 @@
         <v>8000</v>
       </c>
       <c r="C68">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="D68">
-        <v>62.65</v>
+        <v>-561.87</v>
       </c>
       <c r="E68">
-        <v>16480</v>
+        <v>15760</v>
       </c>
       <c r="F68" t="s">
         <v>102</v>
@@ -2664,10 +2664,10 @@
         <v>104</v>
       </c>
       <c r="H68">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I68">
-        <v>12905.49</v>
+        <v>12299.1</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -2678,13 +2678,13 @@
         <v>82</v>
       </c>
       <c r="C69">
-        <v>1791.99</v>
+        <v>1767.02</v>
       </c>
       <c r="D69">
-        <v>-3877.78</v>
+        <v>-2047.54</v>
       </c>
       <c r="E69">
-        <v>146943.18</v>
+        <v>144895.64</v>
       </c>
       <c r="F69" t="s">
         <v>103</v>
@@ -2696,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>146943.18</v>
+        <v>144895.64</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -2707,13 +2707,13 @@
         <v>6440</v>
       </c>
       <c r="C70">
-        <v>429.25</v>
+        <v>424.46</v>
       </c>
       <c r="D70">
-        <v>28529.2</v>
+        <v>-30847.6</v>
       </c>
       <c r="E70">
-        <v>2764370</v>
+        <v>2733522.4</v>
       </c>
       <c r="F70" t="s">
         <v>103</v>
@@ -2725,7 +2725,7 @@
         <v>1</v>
       </c>
       <c r="I70">
-        <v>2764370</v>
+        <v>2733522.4</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -2736,13 +2736,13 @@
         <v>2747</v>
       </c>
       <c r="C71">
-        <v>577.8200000000001</v>
+        <v>572.41</v>
       </c>
       <c r="D71">
-        <v>6977.38</v>
+        <v>-14861.27</v>
       </c>
       <c r="E71">
-        <v>1587271.54</v>
+        <v>1572410.27</v>
       </c>
       <c r="F71" t="s">
         <v>103</v>
@@ -2754,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>1587271.54</v>
+        <v>1572410.27</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -2765,13 +2765,13 @@
         <v>8907</v>
       </c>
       <c r="C72">
-        <v>213.17</v>
+        <v>209.25</v>
       </c>
       <c r="D72">
-        <v>-30640.08</v>
+        <v>-34915.44</v>
       </c>
       <c r="E72">
-        <v>1898705.19</v>
+        <v>1863789.75</v>
       </c>
       <c r="F72" t="s">
         <v>103</v>
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>1898705.19</v>
+        <v>1863789.75</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -2794,13 +2794,13 @@
         <v>18100</v>
       </c>
       <c r="C73">
-        <v>41.17</v>
+        <v>40.29</v>
       </c>
       <c r="D73">
-        <v>-543</v>
+        <v>-15928</v>
       </c>
       <c r="E73">
-        <v>745177</v>
+        <v>729249</v>
       </c>
       <c r="F73" t="s">
         <v>103</v>
@@ -2812,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>745177</v>
+        <v>729249</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -2823,13 +2823,13 @@
         <v>100</v>
       </c>
       <c r="C74">
-        <v>63.55</v>
+        <v>63.29</v>
       </c>
       <c r="D74">
-        <v>80</v>
+        <v>-26</v>
       </c>
       <c r="E74">
-        <v>6355</v>
+        <v>6329</v>
       </c>
       <c r="F74" t="s">
         <v>103</v>
@@ -2841,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>6355</v>
+        <v>6329</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -2852,13 +2852,13 @@
         <v>34</v>
       </c>
       <c r="C75">
-        <v>180.99</v>
+        <v>181.54</v>
       </c>
       <c r="D75">
-        <v>-64.94</v>
+        <v>18.7</v>
       </c>
       <c r="E75">
-        <v>6153.66</v>
+        <v>6172.36</v>
       </c>
       <c r="F75" t="s">
         <v>103</v>
@@ -2870,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="I75">
-        <v>6153.66</v>
+        <v>6172.36</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -2881,13 +2881,13 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>106.8666</v>
+        <v>105.65</v>
       </c>
       <c r="D76">
-        <v>-11.3</v>
+        <v>-12.17</v>
       </c>
       <c r="E76">
-        <v>1068.67</v>
+        <v>1056.5</v>
       </c>
       <c r="F76" t="s">
         <v>103</v>
@@ -2899,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>1068.67</v>
+        <v>1056.5</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -2910,13 +2910,13 @@
         <v>18017</v>
       </c>
       <c r="C77">
-        <v>141.18</v>
+        <v>137.97</v>
       </c>
       <c r="D77">
-        <v>-34592.64</v>
+        <v>-57834.57</v>
       </c>
       <c r="E77">
-        <v>2543640.06</v>
+        <v>2485805.49</v>
       </c>
       <c r="F77" t="s">
         <v>103</v>
@@ -2928,7 +2928,7 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>2543640.06</v>
+        <v>2485805.49</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -2939,13 +2939,13 @@
         <v>8810</v>
       </c>
       <c r="C78">
-        <v>165.89</v>
+        <v>162.71</v>
       </c>
       <c r="D78">
-        <v>43961.9</v>
+        <v>-28015.8</v>
       </c>
       <c r="E78">
-        <v>1461490.9</v>
+        <v>1433475.1</v>
       </c>
       <c r="F78" t="s">
         <v>103</v>
@@ -2957,7 +2957,7 @@
         <v>1</v>
       </c>
       <c r="I78">
-        <v>1461490.9</v>
+        <v>1433475.1</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -2968,13 +2968,13 @@
         <v>24680</v>
       </c>
       <c r="C79">
-        <v>657.55</v>
+        <v>661.5700000000001</v>
       </c>
       <c r="D79">
-        <v>-164862.4</v>
+        <v>99213.60000000001</v>
       </c>
       <c r="E79">
-        <v>16228334</v>
+        <v>16327547.6</v>
       </c>
       <c r="F79" t="s">
         <v>103</v>
@@ -2986,7 +2986,7 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>16228334</v>
+        <v>16327547.6</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -2997,13 +2997,13 @@
         <v>3800</v>
       </c>
       <c r="C80">
-        <v>56.11</v>
+        <v>56.28</v>
       </c>
       <c r="D80">
-        <v>-5358</v>
+        <v>646</v>
       </c>
       <c r="E80">
-        <v>213218</v>
+        <v>213864</v>
       </c>
       <c r="F80" t="s">
         <v>103</v>
@@ -3015,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>213218</v>
+        <v>213864</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -3026,13 +3026,13 @@
         <v>9000</v>
       </c>
       <c r="C81">
-        <v>97.91</v>
+        <v>101.04</v>
       </c>
       <c r="D81">
-        <v>-27360</v>
+        <v>28170</v>
       </c>
       <c r="E81">
-        <v>881190</v>
+        <v>909360</v>
       </c>
       <c r="F81" t="s">
         <v>103</v>
@@ -3044,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>881190</v>
+        <v>909360</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -3055,13 +3055,13 @@
         <v>1820</v>
       </c>
       <c r="C82">
-        <v>175.68</v>
+        <v>172.79</v>
       </c>
       <c r="D82">
-        <v>4186</v>
+        <v>-5259.8</v>
       </c>
       <c r="E82">
-        <v>319737.6</v>
+        <v>314477.8</v>
       </c>
       <c r="F82" t="s">
         <v>103</v>
@@ -3073,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>319737.6</v>
+        <v>314477.8</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -3084,13 +3084,13 @@
         <v>66900</v>
       </c>
       <c r="C83">
-        <v>21.55</v>
+        <v>21.29</v>
       </c>
       <c r="D83">
-        <v>-4714.92</v>
+        <v>-13573.76</v>
       </c>
       <c r="E83">
-        <v>1441695</v>
+        <v>1424301</v>
       </c>
       <c r="F83" t="s">
         <v>102</v>
@@ -3099,10 +3099,10 @@
         <v>104</v>
       </c>
       <c r="H83">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I83">
-        <v>1128991.35</v>
+        <v>1111524.5</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -3113,13 +3113,13 @@
         <v>143200</v>
       </c>
       <c r="C84">
-        <v>31.31</v>
+        <v>31.45</v>
       </c>
       <c r="D84">
-        <v>25776</v>
+        <v>20048</v>
       </c>
       <c r="E84">
-        <v>4483592</v>
+        <v>4503640</v>
       </c>
       <c r="F84" t="s">
         <v>103</v>
@@ -3131,7 +3131,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>4483592</v>
+        <v>4503640</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -3142,13 +3142,13 @@
         <v>10700</v>
       </c>
       <c r="C85">
-        <v>100.117</v>
+        <v>98.95</v>
       </c>
       <c r="D85">
-        <v>10774.9</v>
+        <v>-12486.9</v>
       </c>
       <c r="E85">
-        <v>1071251.9</v>
+        <v>1058765</v>
       </c>
       <c r="F85" t="s">
         <v>103</v>
@@ -3160,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>1071251.9</v>
+        <v>1058765</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -3171,13 +3171,13 @@
         <v>7000</v>
       </c>
       <c r="C86">
-        <v>67.11</v>
+        <v>66.59</v>
       </c>
       <c r="D86">
-        <v>-2590</v>
+        <v>-3640</v>
       </c>
       <c r="E86">
-        <v>469770</v>
+        <v>466130</v>
       </c>
       <c r="F86" t="s">
         <v>103</v>
@@ -3189,7 +3189,7 @@
         <v>1</v>
       </c>
       <c r="I86">
-        <v>469770</v>
+        <v>466130</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -3200,13 +3200,13 @@
         <v>20100</v>
       </c>
       <c r="C87">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="D87">
-        <v>-4020</v>
+        <v>-603</v>
       </c>
       <c r="E87">
-        <v>74973</v>
+        <v>74370</v>
       </c>
       <c r="F87" t="s">
         <v>103</v>
@@ -3218,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="I87">
-        <v>74973</v>
+        <v>74370</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -3229,13 +3229,13 @@
         <v>2</v>
       </c>
       <c r="C88">
-        <v>239.71</v>
+        <v>239.6</v>
       </c>
       <c r="D88">
-        <v>-7.18</v>
+        <v>-0.22</v>
       </c>
       <c r="E88">
-        <v>479.42</v>
+        <v>479.2</v>
       </c>
       <c r="F88" t="s">
         <v>103</v>
@@ -3247,7 +3247,7 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>479.42</v>
+        <v>479.2</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -3258,13 +3258,13 @@
         <v>51700</v>
       </c>
       <c r="C89">
-        <v>35.96</v>
+        <v>35.78</v>
       </c>
       <c r="D89">
-        <v>2429.11</v>
+        <v>-7262.12</v>
       </c>
       <c r="E89">
-        <v>1859132</v>
+        <v>1849826</v>
       </c>
       <c r="F89" t="s">
         <v>102</v>
@@ -3273,10 +3273,10 @@
         <v>104</v>
       </c>
       <c r="H89">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I89">
-        <v>1455886.27</v>
+        <v>1443604.21</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -3287,13 +3287,13 @@
         <v>503600</v>
       </c>
       <c r="C90">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="D90">
-        <v>-31548.73</v>
+        <v>-3929.94</v>
       </c>
       <c r="E90">
-        <v>3348940</v>
+        <v>3343904</v>
       </c>
       <c r="F90" t="s">
         <v>102</v>
@@ -3302,10 +3302,10 @@
         <v>104</v>
       </c>
       <c r="H90">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I90">
-        <v>2622554.91</v>
+        <v>2609582.68</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -3316,13 +3316,13 @@
         <v>1</v>
       </c>
       <c r="C91">
-        <v>93.78</v>
+        <v>93.88</v>
       </c>
       <c r="D91">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
       <c r="E91">
-        <v>93.78</v>
+        <v>93.88</v>
       </c>
       <c r="F91" t="s">
         <v>103</v>
@@ -3334,7 +3334,7 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <v>93.78</v>
+        <v>93.88</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -3345,13 +3345,13 @@
         <v>1600</v>
       </c>
       <c r="C92">
-        <v>164.43</v>
+        <v>168.13</v>
       </c>
       <c r="D92">
-        <v>4064</v>
+        <v>5920</v>
       </c>
       <c r="E92">
-        <v>263088</v>
+        <v>269008</v>
       </c>
       <c r="F92" t="s">
         <v>103</v>
@@ -3363,7 +3363,7 @@
         <v>1</v>
       </c>
       <c r="I92">
-        <v>263088</v>
+        <v>269008</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -3374,13 +3374,13 @@
         <v>6000</v>
       </c>
       <c r="C93">
-        <v>26.1501</v>
+        <v>25.9</v>
       </c>
       <c r="D93">
-        <v>3300.6</v>
+        <v>-1500.6</v>
       </c>
       <c r="E93">
-        <v>156900.6</v>
+        <v>155400</v>
       </c>
       <c r="F93" t="s">
         <v>103</v>
@@ -3392,7 +3392,7 @@
         <v>1</v>
       </c>
       <c r="I93">
-        <v>156900.6</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -3403,13 +3403,13 @@
         <v>21</v>
       </c>
       <c r="C94">
-        <v>305.03</v>
+        <v>306.18</v>
       </c>
       <c r="D94">
-        <v>-365.4</v>
+        <v>24.15</v>
       </c>
       <c r="E94">
-        <v>6405.63</v>
+        <v>6429.78</v>
       </c>
       <c r="F94" t="s">
         <v>103</v>
@@ -3421,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="I94">
-        <v>6405.63</v>
+        <v>6429.78</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -3432,13 +3432,13 @@
         <v>10</v>
       </c>
       <c r="C95">
-        <v>161.12</v>
+        <v>153.79</v>
       </c>
       <c r="D95">
-        <v>-54.6</v>
+        <v>-73.3</v>
       </c>
       <c r="E95">
-        <v>1611.2</v>
+        <v>1537.9</v>
       </c>
       <c r="F95" t="s">
         <v>103</v>
@@ -3450,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <v>1611.2</v>
+        <v>1537.9</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -3461,13 +3461,13 @@
         <v>6003</v>
       </c>
       <c r="C96">
-        <v>47.24</v>
+        <v>46.61</v>
       </c>
       <c r="D96">
-        <v>840.42</v>
+        <v>-3781.89</v>
       </c>
       <c r="E96">
-        <v>283581.72</v>
+        <v>279799.83</v>
       </c>
       <c r="F96" t="s">
         <v>103</v>
@@ -3479,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>283581.72</v>
+        <v>279799.83</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -3490,13 +3490,13 @@
         <v>20000</v>
       </c>
       <c r="C97">
-        <v>143.84</v>
+        <v>142.84</v>
       </c>
       <c r="D97">
-        <v>7600</v>
+        <v>-20000</v>
       </c>
       <c r="E97">
-        <v>2876800</v>
+        <v>2856800</v>
       </c>
       <c r="F97" t="s">
         <v>103</v>
@@ -3508,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>2876800</v>
+        <v>2856800</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -3519,13 +3519,13 @@
         <v>143300</v>
       </c>
       <c r="C98">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="D98">
-        <v>-1122.15</v>
+        <v>-7827.89</v>
       </c>
       <c r="E98">
-        <v>659180</v>
+        <v>649149</v>
       </c>
       <c r="F98" t="s">
         <v>102</v>
@@ -3534,10 +3534,10 @@
         <v>104</v>
       </c>
       <c r="H98">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I98">
-        <v>516203.86</v>
+        <v>506595.88</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -3548,13 +3548,13 @@
         <v>271664</v>
       </c>
       <c r="C99">
-        <v>21.09</v>
+        <v>20.91</v>
       </c>
       <c r="D99">
-        <v>-10866.56</v>
+        <v>-48899.52</v>
       </c>
       <c r="E99">
-        <v>5729393.76</v>
+        <v>5680494.24</v>
       </c>
       <c r="F99" t="s">
         <v>103</v>
@@ -3566,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="I99">
-        <v>5729393.76</v>
+        <v>5680494.24</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -3577,13 +3577,13 @@
         <v>224882</v>
       </c>
       <c r="C100">
-        <v>25.64</v>
+        <v>25.41</v>
       </c>
       <c r="D100">
-        <v>-8995.280000000001</v>
+        <v>-51722.86</v>
       </c>
       <c r="E100">
-        <v>5765974.48</v>
+        <v>5714251.62</v>
       </c>
       <c r="F100" t="s">
         <v>103</v>
@@ -3595,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="I100">
-        <v>5765974.48</v>
+        <v>5714251.62</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -3606,13 +3606,13 @@
         <v>485340</v>
       </c>
       <c r="C101">
-        <v>100.66</v>
+        <v>100.67</v>
       </c>
       <c r="D101">
-        <v>9706.799999999999</v>
+        <v>4853.4</v>
       </c>
       <c r="E101">
-        <v>48854324.4</v>
+        <v>48859177.8</v>
       </c>
       <c r="F101" t="s">
         <v>103</v>
@@ -3624,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="I101">
-        <v>48854324.4</v>
+        <v>48859177.8</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3635,13 +3635,13 @@
         <v>1521</v>
       </c>
       <c r="C102">
-        <v>42.64</v>
+        <v>42.55</v>
       </c>
       <c r="D102">
-        <v>-76.05</v>
+        <v>-136.89</v>
       </c>
       <c r="E102">
-        <v>64855.44</v>
+        <v>64718.55</v>
       </c>
       <c r="F102" t="s">
         <v>103</v>
@@ -3653,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>64855.44</v>
+        <v>64718.55</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3664,13 +3664,13 @@
         <v>5600</v>
       </c>
       <c r="C103">
-        <v>86.37</v>
+        <v>85.7</v>
       </c>
       <c r="D103">
-        <v>504</v>
+        <v>-3752</v>
       </c>
       <c r="E103">
-        <v>483672</v>
+        <v>479920</v>
       </c>
       <c r="F103" t="s">
         <v>103</v>
@@ -3682,7 +3682,7 @@
         <v>1</v>
       </c>
       <c r="I103">
-        <v>483672</v>
+        <v>479920</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3693,13 +3693,13 @@
         <v>790</v>
       </c>
       <c r="C104">
-        <v>110.61</v>
+        <v>106.17</v>
       </c>
       <c r="D104">
-        <v>-5759.1</v>
+        <v>-3507.6</v>
       </c>
       <c r="E104">
-        <v>87381.89999999999</v>
+        <v>83874.3</v>
       </c>
       <c r="F104" t="s">
         <v>103</v>
@@ -3711,7 +3711,7 @@
         <v>1</v>
       </c>
       <c r="I104">
-        <v>87381.89999999999</v>
+        <v>83874.3</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3722,13 +3722,13 @@
         <v>12103</v>
       </c>
       <c r="C105">
-        <v>88.54000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="D105">
-        <v>-49017.15</v>
+        <v>-28078.96</v>
       </c>
       <c r="E105">
-        <v>1071599.62</v>
+        <v>1043520.66</v>
       </c>
       <c r="F105" t="s">
         <v>103</v>
@@ -3740,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="I105">
-        <v>1071599.62</v>
+        <v>1043520.66</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3751,13 +3751,13 @@
         <v>59428</v>
       </c>
       <c r="C106">
-        <v>45.8</v>
+        <v>45.31</v>
       </c>
       <c r="D106">
-        <v>-50513.8</v>
+        <v>-29119.72</v>
       </c>
       <c r="E106">
-        <v>2721802.4</v>
+        <v>2692682.68</v>
       </c>
       <c r="F106" t="s">
         <v>103</v>
@@ -3769,7 +3769,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>2721802.4</v>
+        <v>2692682.68</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3780,13 +3780,13 @@
         <v>6788</v>
       </c>
       <c r="C107">
-        <v>54.23</v>
+        <v>52.89</v>
       </c>
       <c r="D107">
-        <v>-16766.36</v>
+        <v>-9095.92</v>
       </c>
       <c r="E107">
-        <v>368113.24</v>
+        <v>359017.32</v>
       </c>
       <c r="F107" t="s">
         <v>103</v>
@@ -3798,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="I107">
-        <v>368113.24</v>
+        <v>359017.32</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3809,13 +3809,13 @@
         <v>100</v>
       </c>
       <c r="C108">
-        <v>83.02</v>
+        <v>81.55</v>
       </c>
       <c r="D108">
-        <v>-74</v>
+        <v>-147</v>
       </c>
       <c r="E108">
-        <v>8302</v>
+        <v>8155</v>
       </c>
       <c r="F108" t="s">
         <v>103</v>
@@ -3827,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>8302</v>
+        <v>8155</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3838,13 +3838,13 @@
         <v>33850</v>
       </c>
       <c r="C109">
-        <v>57.71</v>
+        <v>59.03</v>
       </c>
       <c r="D109">
-        <v>31819</v>
+        <v>44682</v>
       </c>
       <c r="E109">
-        <v>1953483.5</v>
+        <v>1998165.5</v>
       </c>
       <c r="F109" t="s">
         <v>103</v>
@@ -3856,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>1953483.5</v>
+        <v>1998165.5</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -3867,13 +3867,13 @@
         <v>33</v>
       </c>
       <c r="C110">
-        <v>57.5</v>
+        <v>57.26</v>
       </c>
       <c r="D110">
-        <v>-2.64</v>
+        <v>-7.92</v>
       </c>
       <c r="E110">
-        <v>1897.5</v>
+        <v>1889.58</v>
       </c>
       <c r="F110" t="s">
         <v>103</v>
@@ -3885,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="I110">
-        <v>1897.5</v>
+        <v>1889.58</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -3908,10 +3908,10 @@
         <v>102</v>
       </c>
       <c r="H111">
-        <v>0.7831</v>
+        <v>0.7804</v>
       </c>
       <c r="I111">
-        <v>232.09</v>
+        <v>231.29</v>
       </c>
     </row>
   </sheetData>
